--- a/MCNP/Nuclides.xlsx
+++ b/MCNP/Nuclides.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyWork\MCNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A27DB8-0248-4F6E-9268-26A64FEFBB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850058EA-40DA-47E1-929B-CAA4DB22705A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5E493A83-4E75-40CE-9E48-F182FA9F38C1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{5E493A83-4E75-40CE-9E48-F182FA9F38C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuclides" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3395" uniqueCount="3164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3405" uniqueCount="3172">
   <si>
     <t>n</t>
   </si>
@@ -9529,13 +9552,38 @@
   </si>
   <si>
     <t>Ts294</t>
+  </si>
+  <si>
+    <t>Nuclides</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>T1/2</t>
+  </si>
+  <si>
+    <t>λ</t>
+  </si>
+  <si>
+    <t>500μA-10d</t>
+  </si>
+  <si>
+    <t>cool-10d</t>
+  </si>
+  <si>
+    <t>Nuclides</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9564,6 +9612,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -9587,13 +9644,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9930,12 +10001,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EF9669B-DBAC-4BF4-B805-73AAB1333B1B}">
   <dimension ref="A2:E3163"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="3" width="8.88671875" style="2"/>
-    <col min="4" max="4" width="13.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="3" width="8.875" style="2"/>
+    <col min="4" max="4" width="13.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.875" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -63687,4 +63758,119 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E4CE5F-F5AA-462D-891F-48BAF0FE7197}">
+  <dimension ref="B1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B1" s="3" t="s">
+        <v>3164</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3165</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3166</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3164</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3167</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>3167</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3168</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>3169</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>3170</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>3171</v>
+      </c>
+      <c r="L1" s="5">
+        <v>21</v>
+      </c>
+      <c r="M1" s="5">
+        <v>63</v>
+      </c>
+      <c r="N1" s="5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B2" s="6">
+        <v>11024</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="str">
+        <f>VLOOKUP(B2,Nuclides!A:F,5,FALSE)</f>
+        <v>Na24</v>
+      </c>
+      <c r="F2" s="7">
+        <f>VLOOKUP(B2,Nuclides!A:F,4,FALSE)</f>
+        <v>53989.2</v>
+      </c>
+      <c r="G2" s="8" t="str">
+        <f t="shared" ref="G2" si="0">IF(F2="STABLE", "STABLE", IF(F2&lt;60, F2&amp;"s", IF(F2&lt;3600, ROUND(F2/60,2)&amp;"min", IF(F2&lt;86400, ROUND(F2/3600,2)&amp;"h", IF(F2&lt;31536000, ROUND(F2/86400,2)&amp;"d", ROUND(F2/31536000,2)&amp;"y")))))</f>
+        <v>15h</v>
+      </c>
+      <c r="H2" s="4">
+        <f t="shared" ref="H2" si="1">LN(2)/F2</f>
+        <v>1.2838626624583163E-5</v>
+      </c>
+      <c r="I2" s="4">
+        <f t="shared" ref="I2" si="2">500*6240000000000*C2*(1-EXP(-H2*10*24*3600))</f>
+        <v>3119952.4980788189</v>
+      </c>
+      <c r="J2" s="6">
+        <f t="shared" ref="J2" si="3">I2*EXP(-H2*10*24*3600)</f>
+        <v>47.501197965798788</v>
+      </c>
+      <c r="K2" s="7" t="str">
+        <f t="shared" ref="K2" si="4">E2</f>
+        <v>Na24</v>
+      </c>
+      <c r="L2" s="6" cm="1">
+        <f t="array" ref="L2">SUM(($J2*EXP(-$H2*17*24*3600*_xlfn.SEQUENCE(L$1-1))))+$J2</f>
+        <v>47.501198272736858</v>
+      </c>
+      <c r="M2" s="6" cm="1">
+        <f t="array" ref="M2">SUM(($J2*EXP(-$H2*17*24*3600*_xlfn.SEQUENCE(M$1-1))))+$J2</f>
+        <v>47.501198272736858</v>
+      </c>
+      <c r="N2" s="6" cm="1">
+        <f t="array" ref="N2">SUM(($J2*EXP(-$H2*17*24*3600*_xlfn.SEQUENCE(N$1-1))))+$J2</f>
+        <v>47.501198272736858</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="J2">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/MCNP/Nuclides.xlsx
+++ b/MCNP/Nuclides.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyWork\MCNP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850058EA-40DA-47E1-929B-CAA4DB22705A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5876A6-F9D8-4611-89BB-B98C311CEA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{5E493A83-4E75-40CE-9E48-F182FA9F38C1}"/>
   </bookViews>
@@ -63833,15 +63833,15 @@
         <v>1.2838626624583163E-5</v>
       </c>
       <c r="I2" s="4">
-        <f t="shared" ref="I2" si="2">500*6240000000000*C2*(1-EXP(-H2*10*24*3600))</f>
+        <f>IF(F2="STABLE",C2*500*6240000000000*10*3600,6240000000000*500*C2*(1-EXP(-H2*10*24*3600)))</f>
         <v>3119952.4980788189</v>
       </c>
       <c r="J2" s="6">
-        <f t="shared" ref="J2" si="3">I2*EXP(-H2*10*24*3600)</f>
+        <f t="shared" ref="J2" si="2">I2*EXP(-H2*10*24*3600)</f>
         <v>47.501197965798788</v>
       </c>
       <c r="K2" s="7" t="str">
-        <f t="shared" ref="K2" si="4">E2</f>
+        <f t="shared" ref="K2" si="3">E2</f>
         <v>Na24</v>
       </c>
       <c r="L2" s="6" cm="1">
